--- a/Untitled spreadsheet.xlsx
+++ b/Untitled spreadsheet.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z52"/>
+  <dimension ref="A1:Z57"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="23.71" customWidth="1" style="12" min="1" max="1"/>
@@ -1771,10 +1771,109 @@
       </c>
     </row>
     <row r="53" ht="15.75" customHeight="1" s="12"/>
-    <row r="54" ht="15.75" customHeight="1" s="12"/>
-    <row r="55" ht="15.75" customHeight="1" s="12"/>
-    <row r="56" ht="15.75" customHeight="1" s="12"/>
-    <row r="57" ht="15.75" customHeight="1" s="12"/>
+    <row r="54" ht="15.75" customHeight="1" s="12">
+      <c r="A54" s="0" t="inlineStr">
+        <is>
+          <t>RESULTS — run 2026-06-05 00:36:58  (passed 1/2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="15.75" customHeight="1" s="12">
+      <c r="A55" s="0" t="inlineStr">
+        <is>
+          <t>test_id</t>
+        </is>
+      </c>
+      <c r="B55" s="0" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C55" s="0" t="inlineStr">
+        <is>
+          <t>actual_status</t>
+        </is>
+      </c>
+      <c r="D55" s="0" t="inlineStr">
+        <is>
+          <t>expected_status</t>
+        </is>
+      </c>
+      <c r="E55" s="0" t="inlineStr">
+        <is>
+          <t>correlation_id</t>
+        </is>
+      </c>
+      <c r="F55" s="0" t="inlineStr">
+        <is>
+          <t>detail</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="15.75" customHeight="1" s="12">
+      <c r="A56" s="0" t="inlineStr">
+        <is>
+          <t>TC-001</t>
+        </is>
+      </c>
+      <c r="B56" s="0" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C56" s="0" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="D56" s="0" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="E56" s="0" t="inlineStr">
+        <is>
+          <t>TC-001-540f36356982</t>
+        </is>
+      </c>
+      <c r="F56" s="0" t="inlineStr">
+        <is>
+          <t>logs ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="15.75" customHeight="1" s="12">
+      <c r="A57" s="0" t="inlineStr">
+        <is>
+          <t>TC-002</t>
+        </is>
+      </c>
+      <c r="B57" s="0" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="C57" s="0" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="D57" s="0" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="E57" s="0" t="inlineStr">
+        <is>
+          <t>TC-002-b1c0ab178cf1</t>
+        </is>
+      </c>
+      <c r="F57" s="0" t="inlineStr">
+        <is>
+          <t>missing logs: This is the end log</t>
+        </is>
+      </c>
+    </row>
     <row r="58" ht="15.75" customHeight="1" s="12"/>
     <row r="59" ht="15.75" customHeight="1" s="12"/>
     <row r="60" ht="15.75" customHeight="1" s="12"/>
@@ -2744,7 +2843,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>run 2026-06-04 22:36:06</t>
+          <t>run 2026-06-05 00:36:58</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
@@ -2877,7 +2976,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1256.7</t>
+          <t>885.9</t>
         </is>
       </c>
     </row>
@@ -2904,7 +3003,7 @@
           <t>{
   "status": "ACCEPTED",
   "sku": "ABC-100",
-  "correlationId": "TC-001-426a5187079a"
+  "correlationId": "TC-001-540f36356982"
 }</t>
         </is>
       </c>
@@ -2941,7 +3040,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>TC-001-426a5187079a</t>
+          <t>TC-001-540f36356982</t>
         </is>
       </c>
     </row>
@@ -2989,7 +3088,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-04T17:05:03.903Z INFO [xlwjf] LoggerMessageProcessor event:TC-001-426a5187079a [MuleRuntime].uber.13: [test-eapi].test-eapiFlow.CPU_INTENSIVE @91d86a3 - This is the end log TC-001-426a5187079a</t>
+          <t>2026-06-04T19:05:55.365Z INFO [xlwjf] LoggerMessageProcessor event:TC-001-540f36356982 [MuleRuntime].uber.14: [test-eapi].test-eapiFlow.CPU_INTENSIVE @91d86a3 - This is the end log TC-001-540f36356982</t>
         </is>
       </c>
     </row>
@@ -3001,7 +3100,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-06-04T17:05:03.898Z INFO [xlwjf] LoggerMessageProcessor event:TC-001-426a5187079a [MuleRuntime].uber.01: [test-eapi].test-eapiFlow.CPU_LITE @48d46169 - this is start log TC-001-426a5187079a</t>
+          <t>2026-06-04T19:05:55.363Z INFO [xlwjf] LoggerMessageProcessor event:TC-001-540f36356982 [MuleRuntime].uber.01: [test-eapi].test-eapiFlow.CPU_LITE @48d46169 - this is start log TC-001-540f36356982</t>
         </is>
       </c>
     </row>
@@ -3027,7 +3126,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>run 2026-06-04 22:36:06</t>
+          <t>run 2026-06-05 00:36:58</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
@@ -3159,7 +3258,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>810.6</t>
+          <t>791.6</t>
         </is>
       </c>
     </row>
@@ -3186,7 +3285,7 @@
           <t>{
   "error": "VALIDATION_ERROR",
   "field": "qty",
-  "correlationId": "TC-002-bfebd9f7fa34"
+  "correlationId": "TC-002-b1c0ab178cf1"
 }</t>
         </is>
       </c>
@@ -3223,7 +3322,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>TC-002-bfebd9f7fa34</t>
+          <t>TC-002-b1c0ab178cf1</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3377,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-06-04T17:05:04.862Z INFO [xlwjf] LoggerMessageProcessor event:TC-002-bfebd9f7fa34 [MuleRuntime].uber.13: [test-eapi].test-eapiFlow.CPU_LITE @48d46169 - this is start log TC-002-bfebd9f7fa34</t>
+          <t>2026-06-04T19:05:56.162Z INFO [xlwjf] LoggerMessageProcessor event:TC-002-b1c0ab178cf1 [MuleRuntime].uber.14: [test-eapi].test-eapiFlow.CPU_LITE @48d46169 - this is start log TC-002-b1c0ab178cf1</t>
         </is>
       </c>
     </row>
